--- a/work_request_forms/047_sewer_maintenance_workflow_checklist_form--work_request_forms.xlsx
+++ b/work_request_forms/047_sewer_maintenance_workflow_checklist_form--work_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>work_orders</t>
+          <t>work_order</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Work Orders</t>
+          <t>Work Order</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>site_checks</t>
+          <t>site_check</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Site Checks</t>
+          <t>Site Check</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>safety_reviews</t>
+          <t>safety_review</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Safety Reviews</t>
+          <t>Safety Review</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -875,213 +875,6 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>assigned_to</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Assigned To</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>assigned_by</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Assigned By</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,10 +891,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +919,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>site_checks_choices</t>
+          <t>site_check_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +936,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>site_checks_choices</t>
+          <t>site_check_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +953,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>safety_reviews_choices</t>
+          <t>safety_review_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +970,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>safety_reviews_choices</t>
+          <t>safety_review_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1267,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1077,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>priority_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1111,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1369,165 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>location_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
           <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>assigned_by_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>assigned_by_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>priority_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>priority_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Inactive</t>
         </is>
       </c>
     </row>
